--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35104-2026 artfynd.xlsx
+++ b/artfynd/A 35104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136986277</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136986997</v>
       </c>
       <c r="B3" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136987301</v>
       </c>
       <c r="B4" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
